--- a/视频工作流/_proc/缺口工作表.xlsx
+++ b/视频工作流/_proc/缺口工作表.xlsx
@@ -521,17 +521,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12秒4段片已出│自检6项PASS│里程7.38=0.67*9+0.45*3 误差0│单帧最大跳Z0.0314m│帧间差均值0.187最大0.337无闪烁</t>
+          <t>ADAPT capability function animation timeline scheduler; Behavior Markup Language BML scheduling</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>ADAPT《The Agent Development and Prototyping Testbed》(Shoulson, Marshak, Kapadia, Badler; IEEE TVCG 2013, Rutgers)——body capability 由 choreographer 产出，各自持有 skeleton 私有副本后经 blend node 合成，新增能力只需接入 pose dataflow graph；PBT scheduler 以 30 ticks/s 驱动。时间线分段与同步另参 SAIBA/BML《SmartBody: Behavior Realization for Embodied Conversational Agents》(Thiebaux et al., AAMAS 2008, USC ICT)——behavior &amp; schedule manager 产出分层 motion controller 调度表</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -581,11 +581,13 @@
           <t>inverse kinematics contact constraint biped animation solver</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>IK 残差 &lt;1e-6，关节不超限</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -623,11 +625,13 @@
           <t>prop handoff ownership attachment animation ADAPT PropHandoff</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>道具跟随手，不穿模</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -665,11 +669,13 @@
           <t>facial expression animation blendshape smile mouth corner</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>嘴角上扬可测</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -707,11 +713,13 @@
           <t>finger tap animation hand rig joint chain</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>指尖上下，掌不动</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -749,11 +757,13 @@
           <t>gaze shift head eye movement saccade amplitude formula</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>视线转向目标，头眼时序</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -791,11 +801,13 @@
           <t>crossed legs sitting pose rig IK</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>双腿交叠不穿模</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -833,11 +845,13 @@
           <t>page flip paper deformation animation curve</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>纸面卷曲再落下</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -875,11 +889,13 @@
           <t>prop release placement animation ownership transfer</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>道具脱离手，落到面</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -917,11 +933,13 @@
           <t>reach grasp animation inverse kinematics CCD FABRIK limb</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>手到目标点，肘方向合理</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -959,11 +977,13 @@
           <t>sit down animation IK contact constraint biped; sit to stand STS phase</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>臀贴凳 脚踩地，支撑面内</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1001,11 +1021,13 @@
           <t>stand up animation center of mass transfer STS four phase</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>重心前移→离凳→站直</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1043,11 +1065,13 @@
           <t>2D parallax layer scroll rate depth formula</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>各层速率比 = 深度反比</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1085,11 +1109,13 @@
           <t>camera dolly zoom perspective interpolation formula</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>推近时透视缩放单调递增</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1127,11 +1153,13 @@
           <t>camera pan angular velocity formula horizontal</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>横摇角速度恒定无跳</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1169,11 +1197,13 @@
           <t>shot size framing MLS MS MCU subject height ratio</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>景别切换人物占画面比例达标</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1211,11 +1241,13 @@
           <t>camera tracking follow smoothing deadzone formula</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>跟拍主体保持在框内</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1253,11 +1285,13 @@
           <t>procedural terrazzo floor texture generation</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>地面材质有颗粒</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1295,11 +1329,13 @@
           <t>procedural interior room generation shape grammar; procedural cafe layout</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>室内包可出，层序正确</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1337,11 +1373,13 @@
           <t>light zone falloff inverse square 2D; window light gradient</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>明暗分区可测亮度差</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1379,11 +1417,13 @@
           <t>procedural furniture chair table generation parameter</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>桌椅杯书可实例化</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1421,11 +1461,13 @@
           <t>shape grammar city wall brick generation</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>城墙砖纹可复现</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1463,11 +1505,13 @@
           <t>procedural water ripple gerstner wave 2D animation</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>波纹随时间流动不闪</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1505,11 +1549,13 @@
           <t>dapple light spot caustics animation noise</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>光斑缓慢晃动</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1547,11 +1593,13 @@
           <t>micro expression animation timing duration</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>微表情时长 0.2-0.5s</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1589,11 +1637,13 @@
           <t>paper bend deformation curve animation</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>纸面弯曲可控</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1631,11 +1681,13 @@
           <t>particle system steam rising buoyancy noise formula</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>粒子上升且消散</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1673,11 +1725,13 @@
           <t>procedural face cheekbone geometry shading</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>颧骨有明暗</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1715,11 +1769,13 @@
           <t>cloth layering inner outer garment procedural collar hem</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>内外层可分离</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1757,11 +1813,13 @@
           <t>trouser leg separation from leg procedural</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>裤腿与腿分离</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1799,11 +1857,13 @@
           <t>eyelash drawing procedural eye detail</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>睫毛在眼上沿</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1841,11 +1901,13 @@
           <t>face shape parameterization oval round square procedural</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>脸型参数可切换</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1883,11 +1945,13 @@
           <t>procedural hair strand generation curve ponytail</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>发束跟随头动</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1925,11 +1989,13 @@
           <t>sitting posture leaning forward rig</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>前倾角度可测</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1967,11 +2033,13 @@
           <t>temperament through motion timing pacing</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>节奏参数可调</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2009,11 +2077,13 @@
           <t>procedural ambience sound synthesis noise</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>环境音可出</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2051,11 +2121,13 @@
           <t>foley sound synthesis procedural impact</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>动作音对齐动作时刻</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2093,11 +2165,13 @@
           <t>algorithmic music generation piano background</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>配乐可出</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2135,11 +2209,13 @@
           <t>ARAP as rigid as possible Sorkine Alexa deformation</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>形变保刚性</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2177,11 +2253,13 @@
           <t>bezier limb tapered organic torso procedural character</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>四肢锥形可绘</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2219,11 +2297,13 @@
           <t>BVH motion capture file parse retarget python</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>BVH 可解析重定向</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2261,11 +2341,13 @@
           <t>8 direction sprite body angle perspective walking</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>8 朝向可切</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2303,11 +2385,13 @@
           <t>secondary motion damped spring hair cloth follow</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>二级运动滞后于主体</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2345,11 +2429,13 @@
           <t>Lumo 2D shading normal from silhouette weighted</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>圆被着色成球</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2387,11 +2473,13 @@
           <t>paper cutout shadow offset alpha silhouette</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>阴影偏移一致</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2429,11 +2517,13 @@
           <t>python render mp4 from frame sequence ffmpeg</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>直出 MP4</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2476,6 +2566,8 @@
           <t>build_phase_setup.py 等7处</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2518,6 +2610,8 @@
           <t>_ground_arc.py 等4处</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2560,6 +2654,8 @@
           <t>_camera.py 等2处</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2602,6 +2698,8 @@
           <t>_common.py 等29处</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2644,6 +2742,7 @@
           <t>透视投影相似三角形：路半宽∝1/Z。远端收敛比由 px_per_m(Z) 推出，V4 实测 5.25 倍（非手填）</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>✔</t>
@@ -2691,6 +2790,8 @@
           <t>主链路12处</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2733,6 +2834,8 @@
           <t>_archive_tts 2处</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2775,6 +2878,8 @@
           <t>主链路</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2817,6 +2922,7 @@
           <t>多排矩形剪影 + 中式坡顶，越近越大越暗；LOD 由窗户 grammar 控制</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>✔</t>
@@ -2864,6 +2970,7 @@
           <t>stacked Perlin fBm + smoothstep 阈值，coverage 阈值控云量（0.2→0.6 对应 0.117→0.376 实测单调）</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>✔</t>
@@ -2911,6 +3018,8 @@
           <t>主链路1处</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2953,6 +3062,7 @@
           <t>空气透视参与介质形式：pixel = L_surface*T + L_air；T=exp(-tau)，tau=β·∫density(h)ds，density(h)=0.55·exp(-h/8000)+0.45·exp(-h/1500)（Rayleigh 分子层 + 气溶胶层）。T→0 时地表色收敛于同一视线天空色。metabunk Sitrec Atmospheric Aerial Perspective</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>✔</t>
@@ -3000,6 +3110,7 @@
           <t>midpoint displacement（1D 分形山脊）。Paul Martz, gameprogrammer.com/fractal.html；Fractal Art FAQ 3k。roughness 常量控制衰减，典型 0.5~0.75，越大越嶙峋</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>✔</t>
@@ -3047,6 +3158,7 @@
           <t>Perez / Preetham 1999 天空亮度模型（天顶→地平线渐变）</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>✔</t>
@@ -3094,6 +3206,7 @@
           <t>Honda 1971（Honda &amp; Fisher 1978/1979 沿用）。母枝分出主轴/侧轴，长度比 r1(子/母)、r2，侧轴偏角 θ；r1/r2 决定顶端优势（冠形圆↔锥），θ=30° 示例。ScienceDirect S0022519325000591 复述</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>✔</t>
@@ -3138,9 +3251,10 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>GPU Gems 3 Ch.16《Vegetation Procedural Animation and Shading in Crysis》(NVIDIA)。主弯曲: fBF=vPos.z*fBendScale; fBF+=1; fBF=fBF*fBF-fBF; vNewPos.xy+=vWind.xy*fBF; 再 normalize(vNewPos)*fLength 重缩放。细节弯曲: 频率四元组 (1.975,0.793,0.375,0.193)；vWaves=(frac((t+phase)*f)*2-1)*fSpeed*fDetailFreq 经 SmoothTriangleWave；vWavesSum=vWaves.xz+vWaves.yw；相位 fObjPhase=dot(worldPos.xyz,1) （世界坐标入相位→每株不同步）。CRYENGINE 顶点色 R=边缘不规则摆 G=相位延迟 B=叶片上下</t>
-        </is>
-      </c>
+          <t>GPU Gems 3 Ch.16《Vegetation Procedural Animation and Shading in Crysis》(NVIDIA)。主弯曲: fBF=vPos.z*fBendScale; fBF+=1; fBF=fBF*fBF-fBF; vNewPos.xy+=vWind.xy*fBF; 再 normalize(vNewPos)*fLength 重缩放。细节弯曲: 频率四元组 (1.975,0.793,0.375,0.193)；vWaves=(frac((t+phase)*f)*2-1)*fSpeed*fDetailFreq 经 SmoothTriangleWave；vWavesSum=vWaves.xz+vWaves.yw；相位 fObjPhase=dot(worldPos.xyz,1) （世界坐标入相位→每株不同步）。CRYENGINE 顶点色 R=叶片边缘刚度 G=每叶相位变化 B=叶片整体刚度 A=预计算 AO（原记成“B=叶片上下”，与原文不符，已按 Ch.16 Figure 16-2 更正）</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>✔</t>
@@ -3188,6 +3302,8 @@
           <t>cloth_aero.py wind_force</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3230,6 +3346,8 @@
           <t>wind_response.py / actors.py</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3272,6 +3390,8 @@
           <t>wind_sway.py</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3313,6 +3433,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3323,6 +3444,7 @@
       <c r="B3" t="n">
         <v>11</v>
       </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3333,6 +3455,7 @@
       <c r="B4" t="n">
         <v>5</v>
       </c>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3343,6 +3466,7 @@
       <c r="B5" t="n">
         <v>6</v>
       </c>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3353,6 +3477,7 @@
       <c r="B6" t="n">
         <v>4</v>
       </c>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3363,6 +3488,7 @@
       <c r="B7" t="n">
         <v>8</v>
       </c>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3373,6 +3499,7 @@
       <c r="B8" t="n">
         <v>3</v>
       </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3383,6 +3510,7 @@
       <c r="B9" t="n">
         <v>8</v>
       </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3393,6 +3521,7 @@
       <c r="B10" t="n">
         <v>19</v>
       </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
